--- a/src/views/game/zlzq/cardList/jiaozhuCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/jiaozhuCard/z_level.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11550" windowHeight="10425" firstSheet="2" activeTab="2"/>
+    <workbookView windowWidth="10290" windowHeight="11040" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="帝国" sheetId="5" r:id="rId1"/>
-    <sheet name="蛮石" sheetId="8" r:id="rId2"/>
-    <sheet name="隐秘" sheetId="7" r:id="rId3"/>
-    <sheet name="禅意" sheetId="6" r:id="rId4"/>
+    <sheet name="隐秘" sheetId="7" r:id="rId2"/>
+    <sheet name="蛮石" sheetId="8" r:id="rId3"/>
+    <sheet name="冬神" sheetId="6" r:id="rId4"/>
+    <sheet name="教主" sheetId="9" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="68">
   <si>
     <t>名称</t>
   </si>
@@ -44,13 +45,19 @@
     <t>圣殿斥候</t>
   </si>
   <si>
-    <t>田园守望者</t>
-  </si>
-  <si>
-    <t>增援战线</t>
-  </si>
-  <si>
-    <t>光明惩戒</t>
+    <t>天使琼浆</t>
+  </si>
+  <si>
+    <t>田园守望者1</t>
+  </si>
+  <si>
+    <t>田园守望者2</t>
+  </si>
+  <si>
+    <t>光明惩戒1</t>
+  </si>
+  <si>
+    <t>光明惩戒2</t>
   </si>
   <si>
     <t>小计：</t>
@@ -62,7 +69,10 @@
     <t>圣殿御卫</t>
   </si>
   <si>
-    <t>召集护卫</t>
+    <t>召集护卫1</t>
+  </si>
+  <si>
+    <t>召集护卫2</t>
   </si>
   <si>
     <t>夺取阵地</t>
@@ -98,7 +108,55 @@
     <t>帝国卡等：</t>
   </si>
   <si>
-    <t>愚笨鲸头鹅</t>
+    <t>电流激活</t>
+  </si>
+  <si>
+    <t>沉重否定1</t>
+  </si>
+  <si>
+    <t>沉重否定2</t>
+  </si>
+  <si>
+    <t>全数否定</t>
+  </si>
+  <si>
+    <t>破魔系教授</t>
+  </si>
+  <si>
+    <t>克隆术</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型1</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型2</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型3</t>
+  </si>
+  <si>
+    <t>学仆-塑钢型</t>
+  </si>
+  <si>
+    <t>观星台大预言家</t>
+  </si>
+  <si>
+    <t>米拉方舟</t>
+  </si>
+  <si>
+    <t>No.4希尔伯特</t>
+  </si>
+  <si>
+    <t>No.5咒刃·布雷克</t>
+  </si>
+  <si>
+    <t>鬼童-7号</t>
+  </si>
+  <si>
+    <t>No.2时光·米拉</t>
+  </si>
+  <si>
+    <t>隐秘卡等：</t>
   </si>
   <si>
     <t>旷野祭师1</t>
@@ -107,12 +165,12 @@
     <t>旷野祭师2</t>
   </si>
   <si>
+    <t>高原卫士</t>
+  </si>
+  <si>
     <t>势如破竹</t>
   </si>
   <si>
-    <t>机敏雀鹰</t>
-  </si>
-  <si>
     <t>强行捕猎</t>
   </si>
   <si>
@@ -122,10 +180,13 @@
     <t>诱敌草人</t>
   </si>
   <si>
+    <t>活力仙人掌</t>
+  </si>
+  <si>
     <t>肥鼠晚宴</t>
   </si>
   <si>
-    <t>活力仙人掌</t>
+    <t>高原保卫战</t>
   </si>
   <si>
     <t>飞斧狂人</t>
@@ -140,55 +201,10 @@
     <t>血饮烈斧·凯</t>
   </si>
   <si>
+    <t>原野大祭师·鲁玛</t>
+  </si>
+  <si>
     <t>蛮石卡等：</t>
-  </si>
-  <si>
-    <t>学仆-观测型</t>
-  </si>
-  <si>
-    <t>沉重否定</t>
-  </si>
-  <si>
-    <t>全数否定</t>
-  </si>
-  <si>
-    <t>破魔系教授</t>
-  </si>
-  <si>
-    <t>克隆术1</t>
-  </si>
-  <si>
-    <t>克隆术2</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型1</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型2</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型3</t>
-  </si>
-  <si>
-    <t>学仆-塑钢型</t>
-  </si>
-  <si>
-    <t>幻域秘树</t>
-  </si>
-  <si>
-    <t>观星台大预言家</t>
-  </si>
-  <si>
-    <t>米拉方舟</t>
-  </si>
-  <si>
-    <t>鬼童-7号</t>
-  </si>
-  <si>
-    <t>No.2时光·米拉</t>
-  </si>
-  <si>
-    <t>隐秘卡等：</t>
   </si>
   <si>
     <t>飓风术</t>
@@ -1182,7 +1198,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1190,7 +1206,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1201,7 +1217,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1212,20 +1228,20 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" s="1">
         <v>3</v>
@@ -1234,9 +1250,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
@@ -1245,54 +1261,54 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="1">
-        <v>3</v>
-      </c>
       <c r="C6" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1">
         <v>5</v>
       </c>
       <c r="C7" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:4">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C10" s="1">
         <f>AVERAGE(C2:C7)</f>
-        <v>21.6666666666667</v>
+        <v>21.1666666666667</v>
       </c>
       <c r="D10" s="2"/>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2">
         <v>2</v>
@@ -1301,9 +1317,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2">
         <v>4</v>
@@ -1312,32 +1328,38 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B15" s="2">
         <v>4</v>
       </c>
       <c r="C15" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B16" s="2">
+        <v>4</v>
+      </c>
+      <c r="C16" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="2">
         <v>6</v>
       </c>
-      <c r="C16" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
+      <c r="C17" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2"/>
@@ -1345,34 +1367,28 @@
       <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19" s="2">
-        <f>AVERAGE(C13:C16)</f>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="3">
-        <v>3</v>
-      </c>
-      <c r="C22" s="3">
-        <v>21</v>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="2">
+        <f>AVERAGE(C13:C17)</f>
+        <v>21.6</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B23" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C23" s="3">
         <v>22</v>
@@ -1380,41 +1396,47 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B24" s="3">
         <v>4</v>
       </c>
       <c r="C24" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B25" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B26" s="3">
+        <v>5</v>
+      </c>
+      <c r="C26" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" s="3">
         <v>6</v>
       </c>
-      <c r="C26" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
+      <c r="C27" s="3">
+        <v>22</v>
+      </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3"/>
@@ -1422,27 +1444,32 @@
       <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C29" s="3">
-        <f>AVERAGE(C22:C26)</f>
-        <v>21.2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C32" s="4">
-        <f>AVERAGE(C2:C7,C13:C16,C22:C26)</f>
-        <v>21.3333333333333</v>
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="3">
+        <f>AVERAGE(C23:C27)</f>
+        <v>21.6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" s="4">
+        <f>AVERAGE(C2:C7,C13:C17,C23:C27)</f>
+        <v>21.4375</v>
       </c>
     </row>
   </sheetData>
@@ -1454,7 +1481,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1462,7 +1489,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1473,120 +1500,120 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B2" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B5" s="1">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="1">
+        <f>AVERAGE(C2:C5)</f>
+        <v>19.5</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="2">
         <v>2</v>
       </c>
-      <c r="C5" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="1">
+      <c r="C11" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="2">
+        <v>2</v>
+      </c>
+      <c r="C12" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="2">
         <v>3</v>
       </c>
-      <c r="C6" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="1">
-        <v>4</v>
-      </c>
-      <c r="C7" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="1">
-        <f>AVERAGE(C2:C7)</f>
-        <v>22</v>
-      </c>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="2">
-        <v>2</v>
-      </c>
       <c r="C13" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B15" s="2">
         <v>3</v>
@@ -1595,12 +1622,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" s="2">
         <v>22</v>
@@ -1608,36 +1635,30 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B17" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C17" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B18" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C18" s="2">
         <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" s="2">
-        <v>8</v>
-      </c>
-      <c r="C19" s="2">
-        <v>19</v>
-      </c>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2"/>
@@ -1645,48 +1666,60 @@
       <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" s="2">
-        <f>AVERAGE(C13:C19)</f>
-        <v>20.8571428571429</v>
+      <c r="A21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="2">
+        <f>AVERAGE(C11:C18)</f>
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="3">
+        <v>2</v>
+      </c>
+      <c r="C24" s="3">
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B25" s="3">
         <v>3</v>
       </c>
       <c r="C25" s="3">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B26" s="3">
+        <v>4</v>
+      </c>
+      <c r="C26" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="3">
         <v>5</v>
       </c>
-      <c r="C26" s="3">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
+      <c r="C27" s="3">
+        <v>21</v>
+      </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="3"/>
@@ -1694,27 +1727,32 @@
       <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C29" s="3">
-        <f>AVERAGE(C25:C26)</f>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" s="4">
-        <f>AVERAGE(C2:C7,C13:C19,C25:C26)</f>
-        <v>20.9333333333333</v>
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="3">
+        <f>AVERAGE(C24:C27)</f>
+        <v>21.75</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="4">
+        <f>AVERAGE(C2:C5,C11:C18,C24:C27)</f>
+        <v>21.0625</v>
       </c>
     </row>
   </sheetData>
@@ -1734,7 +1772,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1745,9 +1783,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -1756,98 +1794,98 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B4" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="1">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1">
+        <v>21</v>
+      </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="1">
-        <f>AVERAGE(C2:C4)</f>
-        <v>20.6666666666667</v>
-      </c>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="2">
-        <v>2</v>
-      </c>
-      <c r="C10" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="2">
-        <v>2</v>
-      </c>
-      <c r="C11" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="1">
+        <f>AVERAGE(C2:C6)</f>
+        <v>21.8</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
       </c>
       <c r="C12" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B13" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" s="2">
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B14" s="2">
         <v>3</v>
@@ -1856,9 +1894,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B15" s="2">
         <v>3</v>
@@ -1867,12 +1905,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B16" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C16" s="2">
         <v>22</v>
@@ -1880,7 +1918,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B17" s="2">
         <v>4</v>
@@ -1891,25 +1929,19 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B18" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C18" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19" s="2">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2">
-        <v>22</v>
-      </c>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="2"/>
@@ -1917,42 +1949,48 @@
       <c r="C20" s="2"/>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" s="2">
-        <f>AVERAGE(C10:C19)</f>
-        <v>20.3</v>
+      <c r="A21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="2">
+        <f>AVERAGE(C12:C18)</f>
+        <v>20.5714285714286</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B24" s="3">
+        <v>3</v>
+      </c>
+      <c r="C24" s="3">
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B25" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B26" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C26" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1967,26 +2005,26 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C29" s="3">
-        <f>AVERAGE(C25:C26)</f>
-        <v>21</v>
+        <f>AVERAGE(C24:C26)</f>
+        <v>19.6666666666667</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C4,C10:C19,C25:C26)</f>
-        <v>20.4666666666667</v>
+        <f>AVERAGE(C2:C6,C12:C18,C24:C26)</f>
+        <v>20.8</v>
       </c>
     </row>
   </sheetData>
@@ -2006,7 +2044,7 @@
     <col min="3" max="3" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2017,9 +2055,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -2028,9 +2066,9 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -2039,9 +2077,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -2050,9 +2088,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -2061,9 +2099,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
@@ -2072,9 +2110,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B7" s="1">
         <v>3</v>
@@ -2083,9 +2121,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B8" s="1">
         <v>4</v>
@@ -2094,9 +2132,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B9" s="1">
         <v>4</v>
@@ -2105,9 +2143,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B10" s="1">
         <v>4</v>
@@ -2116,22 +2154,22 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:4">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:4">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C13" s="1">
         <f>AVERAGE(C2:C10)</f>
@@ -2139,9 +2177,9 @@
       </c>
       <c r="D13" s="2"/>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B16" s="2">
         <v>4</v>
@@ -2152,7 +2190,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B17" s="2">
         <v>4</v>
@@ -2163,7 +2201,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B18" s="2">
         <v>4</v>
@@ -2174,7 +2212,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B19" s="2">
         <v>4</v>
@@ -2195,10 +2233,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C22" s="2">
         <f>AVERAGE(C16:C19)</f>
@@ -2207,7 +2245,7 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B25" s="3">
         <v>4</v>
@@ -2218,7 +2256,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B26" s="3">
         <v>4</v>
@@ -2239,10 +2277,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C25:C26)</f>
@@ -2251,10 +2289,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C32" s="4">
         <f>AVERAGE(C2:C10,C16:C19,C25:C26)</f>
@@ -2265,4 +2303,15 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/src/views/game/zlzq/cardList/jiaozhuCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/jiaozhuCard/z_level.xlsx
@@ -4,12 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10290" windowHeight="11040" activeTab="2"/>
+    <workbookView windowWidth="11910" windowHeight="11745" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="帝国" sheetId="5" r:id="rId1"/>
-    <sheet name="隐秘" sheetId="7" r:id="rId2"/>
-    <sheet name="蛮石" sheetId="8" r:id="rId3"/>
+    <sheet name="蛮石" sheetId="8" r:id="rId2"/>
+    <sheet name="隐秘" sheetId="7" r:id="rId3"/>
     <sheet name="冬神" sheetId="6" r:id="rId4"/>
     <sheet name="教主" sheetId="9" r:id="rId5"/>
   </sheets>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="76">
   <si>
     <t>名称</t>
   </si>
@@ -42,9 +42,6 @@
     <t>卡等</t>
   </si>
   <si>
-    <t>圣殿斥候</t>
-  </si>
-  <si>
     <t>天使琼浆</t>
   </si>
   <si>
@@ -54,6 +51,9 @@
     <t>田园守望者2</t>
   </si>
   <si>
+    <t>符文·生命徽记</t>
+  </si>
+  <si>
     <t>光明惩戒1</t>
   </si>
   <si>
@@ -78,6 +78,9 @@
     <t>夺取阵地</t>
   </si>
   <si>
+    <t>皇家射手</t>
+  </si>
+  <si>
     <t>惩戒天使</t>
   </si>
   <si>
@@ -99,6 +102,9 @@
     <t>正阳大主教·伊恩</t>
   </si>
   <si>
+    <t>钢铁统帅·雷蒙德</t>
+  </si>
+  <si>
     <t>橙色卡等：</t>
   </si>
   <si>
@@ -108,13 +114,58 @@
     <t>帝国卡等：</t>
   </si>
   <si>
+    <t>旷野祭师1</t>
+  </si>
+  <si>
+    <t>旷野祭师2</t>
+  </si>
+  <si>
+    <t>势如破竹</t>
+  </si>
+  <si>
+    <t>强行捕猎</t>
+  </si>
+  <si>
+    <t>无畏猎户</t>
+  </si>
+  <si>
+    <t>诱敌草人</t>
+  </si>
+  <si>
+    <t>肥鼠晚宴</t>
+  </si>
+  <si>
+    <t>活力仙人掌</t>
+  </si>
+  <si>
+    <t>飞斧狂人</t>
+  </si>
+  <si>
+    <t>石斧头领</t>
+  </si>
+  <si>
+    <t>贪食白龙</t>
+  </si>
+  <si>
+    <t>旷野游侠·大羽</t>
+  </si>
+  <si>
+    <t>符文·石破天惊</t>
+  </si>
+  <si>
+    <t>血饮烈斧·凯</t>
+  </si>
+  <si>
+    <t>原野大祭师·鲁玛</t>
+  </si>
+  <si>
+    <t>蛮石卡等：</t>
+  </si>
+  <si>
     <t>电流激活</t>
   </si>
   <si>
-    <t>沉重否定1</t>
-  </si>
-  <si>
-    <t>沉重否定2</t>
+    <t>沉重否定</t>
   </si>
   <si>
     <t>全数否定</t>
@@ -123,7 +174,7 @@
     <t>破魔系教授</t>
   </si>
   <si>
-    <t>克隆术</t>
+    <t>克隆术1</t>
   </si>
   <si>
     <t>学仆-脉冲型1</t>
@@ -135,6 +186,9 @@
     <t>学仆-脉冲型3</t>
   </si>
   <si>
+    <t>学仆-猛禽型</t>
+  </si>
+  <si>
     <t>学仆-塑钢型</t>
   </si>
   <si>
@@ -159,79 +213,49 @@
     <t>隐秘卡等：</t>
   </si>
   <si>
-    <t>旷野祭师1</t>
-  </si>
-  <si>
-    <t>旷野祭师2</t>
-  </si>
-  <si>
-    <t>高原卫士</t>
-  </si>
-  <si>
-    <t>势如破竹</t>
-  </si>
-  <si>
-    <t>强行捕猎</t>
-  </si>
-  <si>
-    <t>无畏猎户</t>
-  </si>
-  <si>
-    <t>诱敌草人</t>
-  </si>
-  <si>
-    <t>活力仙人掌</t>
-  </si>
-  <si>
-    <t>肥鼠晚宴</t>
-  </si>
-  <si>
-    <t>高原保卫战</t>
-  </si>
-  <si>
-    <t>飞斧狂人</t>
-  </si>
-  <si>
-    <t>贪食白龙</t>
-  </si>
-  <si>
-    <t>旷野游侠·大羽</t>
-  </si>
-  <si>
-    <t>血饮烈斧·凯</t>
-  </si>
-  <si>
-    <t>原野大祭师·鲁玛</t>
-  </si>
-  <si>
-    <t>蛮石卡等：</t>
-  </si>
-  <si>
-    <t>飓风术</t>
-  </si>
-  <si>
-    <t>长耳庄巧姑</t>
-  </si>
-  <si>
-    <t>连击</t>
-  </si>
-  <si>
-    <t>风卷残云</t>
-  </si>
-  <si>
-    <t>风铃道人</t>
-  </si>
-  <si>
-    <t>蟠桃会</t>
-  </si>
-  <si>
-    <t>墨轩隐士</t>
-  </si>
-  <si>
-    <t>神机玄女·轩</t>
-  </si>
-  <si>
-    <t>悟能禅杖</t>
+    <t>骨爆</t>
+  </si>
+  <si>
+    <t>寒风草人1</t>
+  </si>
+  <si>
+    <t>寒风草人2</t>
+  </si>
+  <si>
+    <t>绝望之地</t>
+  </si>
+  <si>
+    <t>灵魂抽取</t>
+  </si>
+  <si>
+    <t>冬夜使者1</t>
+  </si>
+  <si>
+    <t>冬夜使者2</t>
+  </si>
+  <si>
+    <t>冬夜使者3</t>
+  </si>
+  <si>
+    <t>天寒地冻1</t>
+  </si>
+  <si>
+    <t>天寒地冻2</t>
+  </si>
+  <si>
+    <t>天寒地冻3</t>
+  </si>
+  <si>
+    <t>极夜阴魂</t>
+  </si>
+  <si>
+    <t>严冬修行</t>
+  </si>
+  <si>
+    <t>寒风血刃</t>
+  </si>
+  <si>
+    <t>永夜女王</t>
   </si>
   <si>
     <t>禅意卡等：</t>
@@ -1198,7 +1222,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1222,7 +1246,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1">
         <v>22</v>
@@ -1233,7 +1257,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="1">
         <v>22</v>
@@ -1258,7 +1282,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1302,7 +1326,7 @@
       </c>
       <c r="C10" s="1">
         <f>AVERAGE(C2:C7)</f>
-        <v>21.1666666666667</v>
+        <v>20.5</v>
       </c>
       <c r="D10" s="2"/>
     </row>
@@ -1355,16 +1379,22 @@
         <v>15</v>
       </c>
       <c r="B17" s="2">
+        <v>5</v>
+      </c>
+      <c r="C17" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="2">
         <v>6</v>
       </c>
-      <c r="C17" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
+      <c r="C18" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2"/>
@@ -1372,26 +1402,20 @@
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="2">
-        <f>AVERAGE(C13:C17)</f>
-        <v>21.6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
+      <c r="B21" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="3">
-        <v>3</v>
-      </c>
-      <c r="C23" s="3">
-        <v>22</v>
+      <c r="C21" s="2">
+        <f>AVERAGE(C13:C18)</f>
+        <v>21.6666666666667</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1399,7 +1423,7 @@
         <v>18</v>
       </c>
       <c r="B24" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C24" s="3">
         <v>22</v>
@@ -1413,7 +1437,7 @@
         <v>4</v>
       </c>
       <c r="C25" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1421,10 +1445,10 @@
         <v>20</v>
       </c>
       <c r="B26" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C26" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1432,44 +1456,66 @@
         <v>21</v>
       </c>
       <c r="B27" s="3">
+        <v>5</v>
+      </c>
+      <c r="C27" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" s="3">
         <v>6</v>
       </c>
-      <c r="C27" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
+      <c r="C28" s="3">
+        <v>22</v>
+      </c>
     </row>
     <row r="29" spans="1:3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
+      <c r="A29" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="3">
+        <v>8</v>
+      </c>
+      <c r="C29" s="3">
+        <v>17</v>
+      </c>
     </row>
     <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" s="3">
-        <f>AVERAGE(C23:C27)</f>
-        <v>21.6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B33" s="4" t="s">
+      <c r="B32" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C33" s="4">
-        <f>AVERAGE(C2:C7,C13:C17,C23:C27)</f>
-        <v>21.4375</v>
+      <c r="C32" s="3">
+        <f>AVERAGE(C24:C29)</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C35" s="4">
+        <f>AVERAGE(C2:C7,C13:C18,C24:C29)</f>
+        <v>21.0555555555556</v>
       </c>
     </row>
   </sheetData>
@@ -1479,289 +1525,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
-  <cols>
-    <col min="1" max="1" width="16.375" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="11.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="1">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="1">
-        <v>2</v>
-      </c>
-      <c r="C4" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="1">
-        <v>3</v>
-      </c>
-      <c r="C5" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="1">
-        <f>AVERAGE(C2:C5)</f>
-        <v>19.5</v>
-      </c>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="2">
-        <v>2</v>
-      </c>
-      <c r="C11" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="2">
-        <v>2</v>
-      </c>
-      <c r="C12" s="2">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="2">
-        <v>3</v>
-      </c>
-      <c r="C13" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="2">
-        <v>3</v>
-      </c>
-      <c r="C14" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="2">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="2">
-        <v>4</v>
-      </c>
-      <c r="C16" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="2">
-        <v>5</v>
-      </c>
-      <c r="C17" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="2">
-        <v>7</v>
-      </c>
-      <c r="C18" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" s="2">
-        <f>AVERAGE(C11:C18)</f>
-        <v>21.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="3">
-        <v>2</v>
-      </c>
-      <c r="C24" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="3">
-        <v>3</v>
-      </c>
-      <c r="C25" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="3">
-        <v>4</v>
-      </c>
-      <c r="C26" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="3">
-        <v>5</v>
-      </c>
-      <c r="C27" s="3">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" s="3">
-        <f>AVERAGE(C24:C27)</f>
-        <v>21.75</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C33" s="4">
-        <f>AVERAGE(C2:C5,C11:C18,C24:C27)</f>
-        <v>21.0625</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D32"/>
@@ -1785,7 +1548,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -1796,7 +1559,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -1807,7 +1570,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -1818,25 +1581,19 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="B5" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C5" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="1">
-        <v>4</v>
-      </c>
-      <c r="C6" s="1">
-        <v>21</v>
-      </c>
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1"/>
@@ -1844,26 +1601,32 @@
       <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
+      <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="1">
-        <f>AVERAGE(C2:C6)</f>
-        <v>21.8</v>
-      </c>
-      <c r="D9" s="2"/>
+      <c r="C8" s="1">
+        <f>AVERAGE(C2:C5)</f>
+        <v>21.75</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="2">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
@@ -1874,10 +1637,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="B13" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" s="2">
         <v>22</v>
@@ -1885,21 +1648,21 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="B14" s="2">
         <v>3</v>
       </c>
       <c r="C14" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="B15" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" s="2">
         <v>22</v>
@@ -1907,10 +1670,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B16" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" s="2">
         <v>22</v>
@@ -1918,25 +1681,19 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B17" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C17" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B18" s="2">
-        <v>8</v>
-      </c>
-      <c r="C18" s="2">
-        <v>12</v>
-      </c>
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2"/>
@@ -1944,53 +1701,59 @@
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
+      <c r="A20" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" s="2">
-        <f>AVERAGE(C12:C18)</f>
-        <v>20.5714285714286</v>
+      <c r="B20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="2">
+        <f>AVERAGE(C11:C17)</f>
+        <v>21.4285714285714</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="3">
+        <v>3</v>
+      </c>
+      <c r="C23" s="3">
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B24" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B25" s="3">
         <v>5</v>
       </c>
       <c r="C25" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B26" s="3">
         <v>7</v>
       </c>
       <c r="C26" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2008,23 +1771,317 @@
         <v>9</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C29" s="3">
-        <f>AVERAGE(C24:C26)</f>
-        <v>19.6666666666667</v>
+        <f>AVERAGE(C23:C26)</f>
+        <v>18.75</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B32" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="4">
+        <f>AVERAGE(C2:C5,C11:C17,C23:C26)</f>
+        <v>20.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="16.375" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="11.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="1">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1">
+        <f>AVERAGE(C2:C4)</f>
+        <v>19.6666666666667</v>
+      </c>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="2">
+        <v>2</v>
+      </c>
+      <c r="C10" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B11" s="2">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="2">
+        <v>2</v>
+      </c>
+      <c r="C12" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="2">
+        <v>3</v>
+      </c>
+      <c r="C13" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="2">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="2">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" s="2">
+        <v>3</v>
+      </c>
+      <c r="C16" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="2">
+        <v>4</v>
+      </c>
+      <c r="C17" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="2">
+        <v>5</v>
+      </c>
+      <c r="C18" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="2">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="2">
+        <f>AVERAGE(C10:C19)</f>
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="3">
+        <v>2</v>
+      </c>
+      <c r="C25" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="3">
+        <v>3</v>
+      </c>
+      <c r="C26" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C32" s="4">
-        <f>AVERAGE(C2:C6,C12:C18,C24:C26)</f>
-        <v>20.8</v>
+      <c r="B27" s="3">
+        <v>4</v>
+      </c>
+      <c r="C27" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" s="3">
+        <v>5</v>
+      </c>
+      <c r="C28" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" s="3">
+        <f>AVERAGE(C25:C28)</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C34" s="4">
+        <f>AVERAGE(C2:C4,C10:C19,C25:C28)</f>
+        <v>20.5294117647059</v>
       </c>
     </row>
   </sheetData>
@@ -2057,18 +2114,18 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B2" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -2079,7 +2136,7 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -2090,110 +2147,110 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B5" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" s="1">
-        <v>3</v>
-      </c>
-      <c r="C7" s="1">
-        <v>12</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B8" s="1">
-        <v>4</v>
-      </c>
-      <c r="C8" s="1">
-        <v>18</v>
-      </c>
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B9" s="1">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="C9" s="1">
+        <f>AVERAGE(C2:C6)</f>
+        <v>13.6</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" s="2">
+        <v>2</v>
+      </c>
+      <c r="C12" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="2">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" s="2">
+        <v>2</v>
+      </c>
+      <c r="C14" s="2">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" s="1">
-        <v>4</v>
-      </c>
-      <c r="C10" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="1">
-        <f>AVERAGE(C2:C10)</f>
-        <v>13.1111111111111</v>
-      </c>
-      <c r="D13" s="2"/>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="2">
+        <v>2</v>
+      </c>
+      <c r="C15" s="2">
+        <v>15</v>
+      </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B16" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C16" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B17" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C17" s="2">
         <v>12</v>
@@ -2201,18 +2258,18 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="B18" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C18" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B19" s="2">
         <v>4</v>
@@ -2236,30 +2293,30 @@
         <v>9</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C22" s="2">
-        <f>AVERAGE(C16:C19)</f>
-        <v>13.25</v>
+        <f>AVERAGE(C12:C19)</f>
+        <v>13.5</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B25" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C25" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B26" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C26" s="3">
         <v>15</v>
@@ -2280,23 +2337,23 @@
         <v>9</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C25:C26)</f>
-        <v>16</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C10,C16:C19,C25:C26)</f>
-        <v>13.5333333333333</v>
+        <f>AVERAGE(C2:C6,C12:C19,C25:C26)</f>
+        <v>13.8</v>
       </c>
     </row>
   </sheetData>

--- a/src/views/game/zlzq/cardList/jiaozhuCard/z_level.xlsx
+++ b/src/views/game/zlzq/cardList/jiaozhuCard/z_level.xlsx
@@ -1,15 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\code\keyuanWeb\src\views\game\zlzq\cardList\jiaozhuCard\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="11910" windowHeight="11745" activeTab="3"/>
+    <workbookView windowWidth="12705" windowHeight="9885"/>
   </bookViews>
   <sheets>
     <sheet name="帝国" sheetId="5" r:id="rId1"/>
-    <sheet name="蛮石" sheetId="8" r:id="rId2"/>
-    <sheet name="隐秘" sheetId="7" r:id="rId3"/>
+    <sheet name="隐秘" sheetId="7" r:id="rId2"/>
+    <sheet name="蛮石" sheetId="8" r:id="rId3"/>
     <sheet name="冬神" sheetId="6" r:id="rId4"/>
     <sheet name="教主" sheetId="9" r:id="rId5"/>
   </sheets>
@@ -31,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="73">
   <si>
     <t>名称</t>
   </si>
@@ -51,9 +56,6 @@
     <t>田园守望者2</t>
   </si>
   <si>
-    <t>符文·生命徽记</t>
-  </si>
-  <si>
     <t>光明惩戒1</t>
   </si>
   <si>
@@ -69,10 +71,7 @@
     <t>圣殿御卫</t>
   </si>
   <si>
-    <t>召集护卫1</t>
-  </si>
-  <si>
-    <t>召集护卫2</t>
+    <t>召集护卫</t>
   </si>
   <si>
     <t>夺取阵地</t>
@@ -102,9 +101,6 @@
     <t>正阳大主教·伊恩</t>
   </si>
   <si>
-    <t>钢铁统帅·雷蒙德</t>
-  </si>
-  <si>
     <t>橙色卡等：</t>
   </si>
   <si>
@@ -114,10 +110,64 @@
     <t>帝国卡等：</t>
   </si>
   <si>
-    <t>旷野祭师1</t>
-  </si>
-  <si>
-    <t>旷野祭师2</t>
+    <t>学仆-观测型</t>
+  </si>
+  <si>
+    <t>沉重否定1</t>
+  </si>
+  <si>
+    <t>沉重否定2</t>
+  </si>
+  <si>
+    <t>全数否定</t>
+  </si>
+  <si>
+    <t>隐形术</t>
+  </si>
+  <si>
+    <t>破魔系教授</t>
+  </si>
+  <si>
+    <t>克隆术1</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型1</t>
+  </si>
+  <si>
+    <t>学仆-脉冲型2</t>
+  </si>
+  <si>
+    <t>符文·邪月之夜</t>
+  </si>
+  <si>
+    <t>学仆-塑钢型</t>
+  </si>
+  <si>
+    <t>观星台大预言家</t>
+  </si>
+  <si>
+    <t>米拉方舟</t>
+  </si>
+  <si>
+    <t>No.5咒刃·布雷克</t>
+  </si>
+  <si>
+    <t>鬼童-7号</t>
+  </si>
+  <si>
+    <t>No.2时光·米拉</t>
+  </si>
+  <si>
+    <t>隐秘卡等：</t>
+  </si>
+  <si>
+    <t>愚笨鲸头鹅</t>
+  </si>
+  <si>
+    <t>旷野猎手</t>
+  </si>
+  <si>
+    <t>旷野祭师</t>
   </si>
   <si>
     <t>势如破竹</t>
@@ -132,12 +182,12 @@
     <t>诱敌草人</t>
   </si>
   <si>
+    <t>活力仙人掌</t>
+  </si>
+  <si>
     <t>肥鼠晚宴</t>
   </si>
   <si>
-    <t>活力仙人掌</t>
-  </si>
-  <si>
     <t>飞斧狂人</t>
   </si>
   <si>
@@ -156,72 +206,24 @@
     <t>血饮烈斧·凯</t>
   </si>
   <si>
-    <t>原野大祭师·鲁玛</t>
-  </si>
-  <si>
     <t>蛮石卡等：</t>
   </si>
   <si>
-    <t>电流激活</t>
-  </si>
-  <si>
-    <t>沉重否定</t>
-  </si>
-  <si>
-    <t>全数否定</t>
-  </si>
-  <si>
-    <t>破魔系教授</t>
-  </si>
-  <si>
-    <t>克隆术1</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型1</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型2</t>
-  </si>
-  <si>
-    <t>学仆-脉冲型3</t>
-  </si>
-  <si>
-    <t>学仆-猛禽型</t>
-  </si>
-  <si>
-    <t>学仆-塑钢型</t>
-  </si>
-  <si>
-    <t>观星台大预言家</t>
-  </si>
-  <si>
-    <t>米拉方舟</t>
-  </si>
-  <si>
-    <t>No.4希尔伯特</t>
-  </si>
-  <si>
-    <t>No.5咒刃·布雷克</t>
-  </si>
-  <si>
-    <t>鬼童-7号</t>
-  </si>
-  <si>
-    <t>No.2时光·米拉</t>
-  </si>
-  <si>
-    <t>隐秘卡等：</t>
-  </si>
-  <si>
     <t>骨爆</t>
   </si>
   <si>
+    <t>寒铁军士</t>
+  </si>
+  <si>
     <t>寒风草人1</t>
   </si>
   <si>
     <t>寒风草人2</t>
   </si>
   <si>
+    <t>极地狂信者</t>
+  </si>
+  <si>
     <t>绝望之地</t>
   </si>
   <si>
@@ -234,16 +236,10 @@
     <t>冬夜使者2</t>
   </si>
   <si>
-    <t>冬夜使者3</t>
-  </si>
-  <si>
     <t>天寒地冻1</t>
   </si>
   <si>
     <t>天寒地冻2</t>
-  </si>
-  <si>
-    <t>天寒地冻3</t>
   </si>
   <si>
     <t>极夜阴魂</t>
@@ -1222,7 +1218,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.375" customWidth="1"/>
@@ -1260,7 +1256,7 @@
         <v>3</v>
       </c>
       <c r="C3" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1271,7 +1267,7 @@
         <v>3</v>
       </c>
       <c r="C4" s="1">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1279,10 +1275,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1293,19 +1289,13 @@
         <v>5</v>
       </c>
       <c r="C6" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="1">
-        <v>5</v>
-      </c>
-      <c r="C7" s="1">
-        <v>19</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1"/>
@@ -1313,32 +1303,38 @@
       <c r="C8" s="1"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C9" s="1">
+        <f>AVERAGE(C2:C6)</f>
+        <v>22</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="1">
-        <f>AVERAGE(C2:C7)</f>
-        <v>20.5</v>
-      </c>
-      <c r="D10" s="2"/>
+      <c r="B12" s="2">
+        <v>2</v>
+      </c>
+      <c r="C12" s="2">
+        <v>24</v>
+      </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C13" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1349,7 +1345,7 @@
         <v>4</v>
       </c>
       <c r="C14" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1357,10 +1353,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C15" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1368,54 +1364,54 @@
         <v>14</v>
       </c>
       <c r="B16" s="2">
+        <v>6</v>
+      </c>
+      <c r="C16" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="2">
+        <f>AVERAGE(C12:C16)</f>
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="3">
+        <v>3</v>
+      </c>
+      <c r="C22" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="3">
         <v>4</v>
       </c>
-      <c r="C16" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2">
-        <v>5</v>
-      </c>
-      <c r="C17" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2">
-        <v>6</v>
-      </c>
-      <c r="C18" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="2">
-        <f>AVERAGE(C13:C18)</f>
-        <v>21.6666666666667</v>
+      <c r="C23" s="3">
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1423,10 +1419,10 @@
         <v>18</v>
       </c>
       <c r="B24" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C24" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1434,10 +1430,10 @@
         <v>19</v>
       </c>
       <c r="B25" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1445,77 +1441,44 @@
         <v>20</v>
       </c>
       <c r="B26" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C26" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B27" s="3">
-        <v>5</v>
-      </c>
-      <c r="C27" s="3">
-        <v>22</v>
-      </c>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
     </row>
     <row r="28" spans="1:3">
-      <c r="A28" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" s="3">
-        <v>6</v>
-      </c>
-      <c r="C28" s="3">
-        <v>22</v>
-      </c>
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" s="3">
+        <f>AVERAGE(C22:C26)</f>
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B29" s="3">
-        <v>8</v>
-      </c>
-      <c r="C29" s="3">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C32" s="3">
-        <f>AVERAGE(C24:C29)</f>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C35" s="4">
-        <f>AVERAGE(C2:C7,C13:C18,C24:C29)</f>
-        <v>21.0555555555556</v>
+      <c r="C32" s="4">
+        <f>AVERAGE(C2:C6,C12:C16,C22:C26)</f>
+        <v>22.4666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1525,6 +1488,300 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:D34"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="1" max="1" width="16.375" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="11.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="1">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="1">
+        <v>3</v>
+      </c>
+      <c r="C5" s="1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="1">
+        <f>AVERAGE(C2:C5)</f>
+        <v>20.75</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="2">
+        <v>2</v>
+      </c>
+      <c r="C12" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="2">
+        <v>2</v>
+      </c>
+      <c r="C13" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="2">
+        <v>2</v>
+      </c>
+      <c r="C14" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="2">
+        <v>3</v>
+      </c>
+      <c r="C15" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="2">
+        <v>3</v>
+      </c>
+      <c r="C16" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="2">
+        <v>3</v>
+      </c>
+      <c r="C17" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="2">
+        <v>4</v>
+      </c>
+      <c r="C18" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="2">
+        <v>5</v>
+      </c>
+      <c r="C19" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="2">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="2">
+        <f>AVERAGE(C11:C20)</f>
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="3">
+        <v>3</v>
+      </c>
+      <c r="C26" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="3">
+        <v>4</v>
+      </c>
+      <c r="C27" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="3">
+        <v>5</v>
+      </c>
+      <c r="C28" s="3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" s="3">
+        <f>AVERAGE(C26:C28)</f>
+        <v>23.3333333333333</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" s="4">
+        <f>AVERAGE(C2:C5,C11:C20,C26:C28)</f>
+        <v>21.6470588235294</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D32"/>
@@ -1548,10 +1805,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="B2" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C2" s="1">
         <v>22</v>
@@ -1559,18 +1816,18 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -1581,19 +1838,25 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="1">
         <v>4</v>
       </c>
-      <c r="C5" s="1">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
+      <c r="C6" s="1">
+        <v>20</v>
+      </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1"/>
@@ -1601,32 +1864,26 @@
       <c r="C7" s="1"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="1">
-        <f>AVERAGE(C2:C5)</f>
-        <v>21.75</v>
-      </c>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="2">
-        <v>2</v>
-      </c>
-      <c r="C11" s="2">
-        <v>22</v>
-      </c>
+      <c r="C9" s="1">
+        <f>AVERAGE(C2:C6)</f>
+        <v>21.8</v>
+      </c>
+      <c r="D9" s="2"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B12" s="2">
         <v>2</v>
@@ -1637,10 +1894,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="B13" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" s="2">
         <v>22</v>
@@ -1648,52 +1905,58 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="B14" s="2">
         <v>3</v>
       </c>
       <c r="C14" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="B15" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="B16" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="B17" s="2">
+        <v>5</v>
+      </c>
+      <c r="C17" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="2">
         <v>8</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C18" s="2">
         <v>20</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2"/>
@@ -1701,59 +1964,53 @@
       <c r="C19" s="2"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="2">
-        <f>AVERAGE(C11:C17)</f>
-        <v>21.4285714285714</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="3">
-        <v>3</v>
-      </c>
-      <c r="C23" s="3">
-        <v>19</v>
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="2">
+        <f>AVERAGE(C12:C18)</f>
+        <v>21.5714285714286</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B24" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C24" s="3">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B25" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B26" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C26" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1768,320 +2025,26 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C29" s="3">
-        <f>AVERAGE(C23:C26)</f>
-        <v>18.75</v>
+        <f>AVERAGE(C24:C26)</f>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C5,C11:C17,C23:C26)</f>
-        <v>20.8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D34"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
-  <cols>
-    <col min="1" max="1" width="16.375" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="11.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="1">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="1">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="1">
-        <f>AVERAGE(C2:C4)</f>
-        <v>19.6666666666667</v>
-      </c>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="2">
-        <v>2</v>
-      </c>
-      <c r="C10" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B11" s="2">
-        <v>2</v>
-      </c>
-      <c r="C11" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="2">
-        <v>2</v>
-      </c>
-      <c r="C12" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="2">
-        <v>3</v>
-      </c>
-      <c r="C13" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="2">
-        <v>3</v>
-      </c>
-      <c r="C14" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="2">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" s="2">
-        <v>3</v>
-      </c>
-      <c r="C16" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17" s="2">
-        <v>4</v>
-      </c>
-      <c r="C17" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B18" s="2">
-        <v>5</v>
-      </c>
-      <c r="C18" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19" s="2">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" s="2">
-        <f>AVERAGE(C10:C19)</f>
-        <v>20.2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" s="3">
-        <v>2</v>
-      </c>
-      <c r="C25" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26" s="3">
-        <v>3</v>
-      </c>
-      <c r="C26" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B27" s="3">
-        <v>4</v>
-      </c>
-      <c r="C27" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B28" s="3">
-        <v>5</v>
-      </c>
-      <c r="C28" s="3">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C31" s="3">
-        <f>AVERAGE(C25:C28)</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C34" s="4">
-        <f>AVERAGE(C2:C4,C10:C19,C25:C28)</f>
-        <v>20.5294117647059</v>
+        <f>AVERAGE(C2:C6,C12:C18,C24:C26)</f>
+        <v>21.1333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -2114,7 +2077,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -2125,18 +2088,18 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
       </c>
       <c r="C3" s="1">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
@@ -2147,107 +2110,107 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B5" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5" s="1">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6" s="1">
         <v>3</v>
       </c>
       <c r="C6" s="1">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
+      <c r="A7" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1">
+        <v>18</v>
+      </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
+      <c r="A8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="1">
+        <v>3</v>
+      </c>
+      <c r="C8" s="1">
+        <v>16</v>
+      </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="1">
-        <f>AVERAGE(C2:C6)</f>
-        <v>13.6</v>
-      </c>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B12" s="2">
-        <v>2</v>
-      </c>
-      <c r="C12" s="2">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" s="2">
-        <v>2</v>
-      </c>
-      <c r="C13" s="2">
-        <v>14</v>
-      </c>
+      <c r="C11" s="1">
+        <f>AVERAGE(C2:C8)</f>
+        <v>15.4285714285714</v>
+      </c>
+      <c r="D11" s="2"/>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B14" s="2">
         <v>2</v>
       </c>
       <c r="C14" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B15" s="2">
         <v>2</v>
       </c>
       <c r="C15" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B16" s="2">
         <v>2</v>
       </c>
       <c r="C16" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B17" s="2">
         <v>2</v>
@@ -2258,24 +2221,24 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B18" s="2">
         <v>3</v>
       </c>
       <c r="C18" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B19" s="2">
         <v>4</v>
       </c>
       <c r="C19" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2290,36 +2253,36 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C22" s="2">
-        <f>AVERAGE(C12:C19)</f>
-        <v>13.5</v>
+        <f>AVERAGE(C14:C19)</f>
+        <v>15.1666666666667</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B25" s="3">
         <v>3</v>
       </c>
       <c r="C25" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B26" s="3">
         <v>5</v>
       </c>
       <c r="C26" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -2334,26 +2297,26 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C29" s="3">
         <f>AVERAGE(C25:C26)</f>
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C32" s="4">
-        <f>AVERAGE(C2:C6,C12:C19,C25:C26)</f>
-        <v>13.8</v>
+        <f>AVERAGE(C2:C8,C14:C19,C25:C26)</f>
+        <v>15.4666666666667</v>
       </c>
     </row>
   </sheetData>
